--- a/test_session/mapped_elements_works.xlsx
+++ b/test_session/mapped_elements_works.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>Element_Index</t>
   </si>
@@ -166,9 +166,6 @@
     <t>W4</t>
   </si>
   <si>
-    <t>Монтаж/демонтаж опалубки</t>
-  </si>
-  <si>
     <t>Гидрошпонка</t>
   </si>
   <si>
@@ -187,12 +184,6 @@
     <t>Подготовка песчаная</t>
   </si>
   <si>
-    <t>Монтаж/демонтаж опалубки лестничных маршей</t>
-  </si>
-  <si>
-    <t>Монтаж/демонтаж опалубки лестничных площадок</t>
-  </si>
-  <si>
     <t>Установка химических анкеров</t>
   </si>
   <si>
@@ -220,9 +211,6 @@
     <t>Бетонирование монолитных железобетонных конструкций парапетов</t>
   </si>
   <si>
-    <t>м2</t>
-  </si>
-  <si>
     <t>м</t>
   </si>
   <si>
@@ -238,9 +226,6 @@
     <t>шт</t>
   </si>
   <si>
-    <t>3.6-70-3</t>
-  </si>
-  <si>
     <t>3.7-19-2</t>
   </si>
   <si>
@@ -253,12 +238,6 @@
     <t>3.8-1-1</t>
   </si>
   <si>
-    <t>3.6-74-5</t>
-  </si>
-  <si>
-    <t>3.6-74-4</t>
-  </si>
-  <si>
     <t>3.9-72-1</t>
   </si>
   <si>
@@ -271,9 +250,6 @@
     <t>3.6-77-4</t>
   </si>
   <si>
-    <t>Монтаж опалубки монолитных железобетонных конструкций фундаментных плит</t>
-  </si>
-  <si>
     <t>Заполнение вертикальных швов стеновых панелей упругими прокладками</t>
   </si>
   <si>
@@ -286,12 +262,6 @@
     <t>Испытание погруженных свай статической нагрузкой в котловане</t>
   </si>
   <si>
-    <t>Монтаж опалубки монолитных железобетонных конструкций лестничных маршей подземной и цокольной частей здания</t>
-  </si>
-  <si>
-    <t>Монтаж опалубки монолитных железобетонных конструкций перекрытия подземной и цокольной частей здания</t>
-  </si>
-  <si>
     <t>Установка химических анкеров в готовые отверстия</t>
   </si>
   <si>
@@ -304,16 +274,10 @@
     <t>Бетонирование по схеме "кран-бадья" монолитных железобетонных конструкций стен подземной и цокольной частей здания, толщина до 300 мм</t>
   </si>
   <si>
-    <t>(P*t)/100</t>
-  </si>
-  <si>
     <t>кол-во</t>
   </si>
   <si>
     <t>S*t</t>
-  </si>
-  <si>
-    <t>(l*b)/100</t>
   </si>
   <si>
     <t>(l*b*t)/100</t>
@@ -683,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -795,16 +759,13 @@
         <v>50</v>
       </c>
       <c r="Q2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="R2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="S2" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -851,13 +812,13 @@
         <v>51</v>
       </c>
       <c r="Q3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="R3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="S3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -904,13 +865,7 @@
         <v>52</v>
       </c>
       <c r="Q4" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" t="s">
-        <v>76</v>
-      </c>
-      <c r="S4" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -956,8 +911,11 @@
       <c r="P5" t="s">
         <v>53</v>
       </c>
-      <c r="Q5" t="s">
-        <v>71</v>
+      <c r="R5" t="s">
+        <v>70</v>
+      </c>
+      <c r="S5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -1003,11 +961,17 @@
       <c r="P6" t="s">
         <v>54</v>
       </c>
+      <c r="Q6" t="s">
+        <v>66</v>
+      </c>
       <c r="R6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S6" t="s">
-        <v>88</v>
+        <v>81</v>
+      </c>
+      <c r="T6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -1054,16 +1018,16 @@
         <v>55</v>
       </c>
       <c r="Q7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="S7" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="T7" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1110,16 +1074,13 @@
         <v>56</v>
       </c>
       <c r="Q8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="S8" t="s">
-        <v>62</v>
-      </c>
-      <c r="T8" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1169,13 +1130,13 @@
         <v>68</v>
       </c>
       <c r="R9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="S9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="T9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1225,10 +1186,13 @@
         <v>68</v>
       </c>
       <c r="R10" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="S10" t="s">
-        <v>91</v>
+        <v>59</v>
+      </c>
+      <c r="T10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1275,315 +1239,261 @@
         <v>59</v>
       </c>
       <c r="Q11" t="s">
+        <v>68</v>
+      </c>
+      <c r="R11" t="s">
         <v>73</v>
       </c>
-      <c r="R11" t="s">
-        <v>81</v>
-      </c>
       <c r="S11" t="s">
-        <v>92</v>
+        <v>59</v>
+      </c>
+      <c r="T11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
         <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
         <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12">
+        <v>7.5</v>
+      </c>
+      <c r="K12">
+        <v>0.3</v>
+      </c>
+      <c r="N12">
         <v>5</v>
       </c>
-      <c r="K12">
-        <v>0.5</v>
-      </c>
-      <c r="N12">
-        <v>10</v>
-      </c>
       <c r="O12">
-        <v>10</v>
-      </c>
-      <c r="P12" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>72</v>
-      </c>
-      <c r="R12" t="s">
-        <v>82</v>
-      </c>
-      <c r="S12" t="s">
-        <v>93</v>
-      </c>
-      <c r="T12" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J13">
-        <v>5</v>
-      </c>
-      <c r="K13">
-        <v>0.5</v>
-      </c>
-      <c r="N13">
-        <v>10</v>
-      </c>
-      <c r="O13">
-        <v>10</v>
-      </c>
-      <c r="P13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>72</v>
-      </c>
-      <c r="R13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S13" t="s">
-        <v>62</v>
-      </c>
-      <c r="T13" t="s">
-        <v>101</v>
+        <v>0.48</v>
+      </c>
+      <c r="L13">
+        <v>0.4</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J14">
-        <v>5</v>
-      </c>
-      <c r="K14">
-        <v>0.5</v>
-      </c>
-      <c r="N14">
-        <v>10</v>
-      </c>
-      <c r="O14">
-        <v>10</v>
+        <v>0.48</v>
+      </c>
+      <c r="L14">
+        <v>0.4</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
       </c>
       <c r="P14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q14" t="s">
-        <v>72</v>
-      </c>
-      <c r="R14" t="s">
-        <v>78</v>
-      </c>
-      <c r="S14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="T14" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
-      </c>
-      <c r="H15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J15">
-        <v>7.5</v>
-      </c>
-      <c r="K15">
+        <v>0.72</v>
+      </c>
+      <c r="L15">
         <v>0.3</v>
       </c>
+      <c r="M15">
+        <v>0.4</v>
+      </c>
       <c r="N15">
-        <v>5</v>
-      </c>
-      <c r="O15">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J16">
-        <v>0.48</v>
-      </c>
-      <c r="L16">
-        <v>0.4</v>
-      </c>
-      <c r="M16">
-        <v>3</v>
+        <v>1.6</v>
+      </c>
+      <c r="K16">
+        <v>0.2</v>
+      </c>
+      <c r="N16">
+        <v>8</v>
+      </c>
+      <c r="O16">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
         <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J17">
-        <v>0.48</v>
-      </c>
-      <c r="L17">
-        <v>0.4</v>
-      </c>
-      <c r="M17">
-        <v>3</v>
+        <v>1.6</v>
+      </c>
+      <c r="K17">
+        <v>0.2</v>
+      </c>
+      <c r="N17">
+        <v>8</v>
+      </c>
+      <c r="O17">
+        <v>40</v>
       </c>
       <c r="P17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q17" t="s">
-        <v>72</v>
+        <v>68</v>
+      </c>
+      <c r="R17" t="s">
+        <v>76</v>
+      </c>
+      <c r="S17" t="s">
+        <v>84</v>
       </c>
       <c r="T17" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1592,30 +1502,33 @@
         <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
         <v>43</v>
       </c>
       <c r="J18">
-        <v>0.72</v>
-      </c>
-      <c r="L18">
-        <v>0.3</v>
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>0.25</v>
       </c>
       <c r="M18">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="O18">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -1624,30 +1537,42 @@
         <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s">
         <v>43</v>
       </c>
       <c r="J19">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>0.2</v>
+        <v>0.25</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="P19" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>68</v>
+      </c>
+      <c r="T19" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -1656,37 +1581,40 @@
         <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
         <v>43</v>
       </c>
       <c r="J20">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>0.2</v>
+        <v>0.25</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O20">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="P20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="R20" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="S20" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="T20" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -1723,149 +1651,20 @@
       <c r="O21">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" t="s">
-        <v>43</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22">
-        <v>0.25</v>
-      </c>
-      <c r="M22">
-        <v>3</v>
-      </c>
-      <c r="N22">
-        <v>4</v>
-      </c>
-      <c r="O22">
-        <v>12</v>
-      </c>
-      <c r="P22" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>72</v>
-      </c>
-      <c r="T22" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" t="s">
-        <v>43</v>
-      </c>
-      <c r="J23">
-        <v>3</v>
-      </c>
-      <c r="K23">
-        <v>0.25</v>
-      </c>
-      <c r="M23">
-        <v>3</v>
-      </c>
-      <c r="N23">
-        <v>4</v>
-      </c>
-      <c r="O23">
-        <v>12</v>
-      </c>
-      <c r="P23" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>72</v>
-      </c>
-      <c r="R23" t="s">
-        <v>84</v>
-      </c>
-      <c r="S23" t="s">
-        <v>95</v>
-      </c>
-      <c r="T23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" t="s">
-        <v>43</v>
-      </c>
-      <c r="J24">
-        <v>3</v>
-      </c>
-      <c r="K24">
-        <v>0.25</v>
-      </c>
-      <c r="M24">
-        <v>3</v>
-      </c>
-      <c r="N24">
-        <v>4</v>
-      </c>
-      <c r="O24">
-        <v>12</v>
-      </c>
-      <c r="P24" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>72</v>
-      </c>
-      <c r="R24" t="s">
-        <v>84</v>
-      </c>
-      <c r="S24" t="s">
-        <v>95</v>
-      </c>
-      <c r="T24" t="s">
-        <v>103</v>
+      <c r="P21" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>68</v>
+      </c>
+      <c r="R21" t="s">
+        <v>77</v>
+      </c>
+      <c r="S21" t="s">
+        <v>85</v>
+      </c>
+      <c r="T21" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
